--- a/public/contoh-jadwal.xlsx
+++ b/public/contoh-jadwal.xlsx
@@ -397,7 +397,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D27"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -474,13 +480,13 @@
         <v>Keberangkatan</v>
       </c>
       <c r="B6" t="str">
-        <v>GIA 581</v>
+        <v>PK SNH</v>
       </c>
       <c r="C6" t="str">
-        <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
+        <v>BANDAR UDARA MARATUA (RTU)</v>
       </c>
       <c r="D6" t="str">
-        <v>12:20</v>
+        <v>11:10</v>
       </c>
     </row>
     <row r="7">
@@ -488,88 +494,298 @@
         <v>Keberangkatan</v>
       </c>
       <c r="B7" t="str">
-        <v>BTK 6257</v>
+        <v>WON 1480</v>
       </c>
       <c r="C7" t="str">
-        <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
+        <v>BANDAR UDARA SYAMSUDIN NOOR (BDJ)</v>
       </c>
       <c r="D7" t="str">
-        <v>13:00</v>
+        <v>11:25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Kedatangan</v>
+        <v>Keberangkatan</v>
       </c>
       <c r="B8" t="str">
-        <v>WON 1481</v>
+        <v>GIA 581</v>
       </c>
       <c r="C8" t="str">
-        <v>BANDAR UDARA SYAMSUDIN NOOR (BDJ)</v>
+        <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
       </c>
       <c r="D8" t="str">
-        <v>08:20</v>
+        <v>12:20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Kedatangan</v>
+        <v>Keberangkatan</v>
       </c>
       <c r="B9" t="str">
-        <v>SJV 640</v>
+        <v>SJV 653</v>
       </c>
       <c r="C9" t="str">
         <v>BANDAR UDARA JUANDA (SUB)</v>
       </c>
       <c r="D9" t="str">
-        <v>08:40</v>
+        <v>12:30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Kedatangan</v>
+        <v>Keberangkatan</v>
       </c>
       <c r="B10" t="str">
-        <v>CTV 460</v>
+        <v>BTK 6257</v>
       </c>
       <c r="C10" t="str">
-        <v>BANDAR UDARA JUANDA (SUB)</v>
+        <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
       </c>
       <c r="D10" t="str">
-        <v>10:30</v>
+        <v>13:00</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Kedatangan</v>
+        <v>Keberangkatan</v>
       </c>
       <c r="B11" t="str">
-        <v>GIA 580</v>
+        <v>WON 1484</v>
       </c>
       <c r="C11" t="str">
-        <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
+        <v>BANDAR UDARA KALIMARAU (BEJ)</v>
       </c>
       <c r="D11" t="str">
-        <v>11:20</v>
+        <v>14:05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Kedatangan</v>
+        <v>Keberangkatan</v>
       </c>
       <c r="B12" t="str">
+        <v>SJV 641</v>
+      </c>
+      <c r="C12" t="str">
+        <v>BANDAR UDARA JUANDA (SUB)</v>
+      </c>
+      <c r="D12" t="str">
+        <v>14:40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Keberangkatan</v>
+      </c>
+      <c r="B13" t="str">
+        <v>CTV 423</v>
+      </c>
+      <c r="C13" t="str">
+        <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>15:00</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Keberangkatan</v>
+      </c>
+      <c r="B14" t="str">
+        <v>BTK 6677</v>
+      </c>
+      <c r="C14" t="str">
+        <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>17:35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B15" t="str">
+        <v>WON 1481</v>
+      </c>
+      <c r="C15" t="str">
+        <v>BANDAR UDARA SYAMSUDIN NOOR (BDJ)</v>
+      </c>
+      <c r="D15" t="str">
+        <v>08:20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B16" t="str">
+        <v>SJV 640</v>
+      </c>
+      <c r="C16" t="str">
+        <v>BANDAR UDARA JUANDA (SUB)</v>
+      </c>
+      <c r="D16" t="str">
+        <v>08:40</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B17" t="str">
+        <v>CTV 460</v>
+      </c>
+      <c r="C17" t="str">
+        <v>BANDAR UDARA JUANDA (SUB)</v>
+      </c>
+      <c r="D17" t="str">
+        <v>10:30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B18" t="str">
+        <v>PK SNH</v>
+      </c>
+      <c r="C18" t="str">
+        <v>BANDAR UDARA LONG APUNG (LPU)</v>
+      </c>
+      <c r="D18" t="str">
+        <v>10:50</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B19" t="str">
+        <v>WON 1479</v>
+      </c>
+      <c r="C19" t="str">
+        <v>BANDAR UDARA MELALAN (GHS)</v>
+      </c>
+      <c r="D19" t="str">
+        <v>11:00</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B20" t="str">
+        <v>GIA 580</v>
+      </c>
+      <c r="C20" t="str">
+        <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
+      </c>
+      <c r="D20" t="str">
+        <v>11:20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SJV 652</v>
+      </c>
+      <c r="C21" t="str">
+        <v>BANDAR UDARA JUANDA (SUB)</v>
+      </c>
+      <c r="D21" t="str">
+        <v>11:50</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B22" t="str">
         <v>BTK 6256</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C22" t="str">
         <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D22" t="str">
         <v>12:20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B23" t="str">
+        <v>WON 1485</v>
+      </c>
+      <c r="C23" t="str">
+        <v>BANDAR UDARA KALIMARAU (BEJ)</v>
+      </c>
+      <c r="D23" t="str">
+        <v>13:35</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B24" t="str">
+        <v>PK SNH</v>
+      </c>
+      <c r="C24" t="str">
+        <v>BANDAR UDARA MARATUA (RTU)</v>
+      </c>
+      <c r="D24" t="str">
+        <v>13:50</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B25" t="str">
+        <v>SJV 658</v>
+      </c>
+      <c r="C25" t="str">
+        <v>BANDAR UDARA YOGYAKARTA (YIA)</v>
+      </c>
+      <c r="D25" t="str">
+        <v>14:00</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B26" t="str">
+        <v>CTV 422</v>
+      </c>
+      <c r="C26" t="str">
+        <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
+      </c>
+      <c r="D26" t="str">
+        <v>14:30</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Kedatangan</v>
+      </c>
+      <c r="B27" t="str">
+        <v>BTK 6676</v>
+      </c>
+      <c r="C27" t="str">
+        <v>BANDAR UDARA SOEKARNO HATTA (CGK)</v>
+      </c>
+      <c r="D27" t="str">
+        <v>16:55</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D27"/>
   </ignoredErrors>
 </worksheet>
 </file>